--- a/dataset/Faulty/free_null_pointer.xlsx
+++ b/dataset/Faulty/free_null_pointer.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/free_null_pointer.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/free_null_pointer.c</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -456,14 +456,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/free_null_pointer.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/free_null_pointer.c</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -478,14 +478,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/free_null_pointer.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/free_null_pointer.c</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,14 +500,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/free_null_pointer.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/free_null_pointer.c</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -522,14 +522,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/free_null_pointer.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/free_null_pointer.c</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/free_null_pointer.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/free_null_pointer.c</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/free_null_pointer.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/free_null_pointer.c</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -588,14 +588,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/free_null_pointer.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/free_null_pointer.c</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -610,14 +610,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/free_null_pointer.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/free_null_pointer.c</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -632,14 +632,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/free_null_pointer.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/free_null_pointer.c</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -649,19 +649,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>#define SET_MEM 0 int *free_null_pointer_002_gbl_ptr = NULL; char **free_null_pointer_010_gbl_dst=NULL; static unsigned char a =INDEX; char * free_null_pointer_005_gbl_ptr; long ** free_null_pointer_007_gbl_doubleptr; enum {min_buffer = 0 , max_buffer = 5 }; static unsigned int min=min_buffer+2; static unsigned int max=max_buffer+2; char **free_null_pointer_009dst; static free_null_pointer_011_u_001 *u; free_null_pointer_014_s_001 *free_null_pointer_014_gbl_s=NULL; extern volatile int vflag; void free_null_pointer_010 () { char str2[][15] = {{"STRING"}, {"TEST"},{"STRING#"},{"TEST!"},{"TRIAL"}}; free_null_pointer_010_func_001(); free_null_pointer_010_func_002(free_null_pointer_010_gbl_dst,str2); free_null_pointer_010_func_003(); } define SET_MEM 0 void free_null_pointer_010_func_001() { int i; { while(SET_MEM) { free_null_pointer_010_gbl_dst = (char**) malloc(5*sizeof(char*)); for(i=0;i&lt;5;i++) { free_null_pointer_010_gbl_dst[i]=(char*) malloc(15*sizeof(char)); } break; } } } void free_null_pointer_010_func_003() { int i; while(SET_MEM) { for(i=0;i&lt;5;i++) { free(free_null_pointer_010_gbl_dst[i]); free_null_pointer_010_gbl_dst[i] = NULL; } break; } while(SET_MEM == 0) { free(free_null_pointer_010_gbl_dst); free_null_pointer_010_gbl_dst = NULL;/*ERROR:Freeing a NULL pointer*/ break; } }</t>
+          <t>#define SET_MEM 0 int *free_null_pointer_002_gbl_ptr = NULL; char **free_null_pointer_010_gbl_dst=NULL; static unsigned char a =INDEX; char * free_null_pointer_005_gbl_ptr; long ** free_null_pointer_007_gbl_doubleptr; enum {min_buffer = 0 , max_buffer = 5 }; static unsigned int min=min_buffer+2; static unsigned int max=max_buffer+2; char **free_null_pointer_009dst; static free_null_pointer_011_u_001 *u; free_null_pointer_014_s_001 *free_null_pointer_014_gbl_s=NULL; extern volatile int vflag; void free_null_pointer_010 () { char str2[][15] = {{"STRING"}, {"TEST"},{"STRING#"},{"TEST!"},{"TRIAL"}}; free_null_pointer_010_func_001(); free_null_pointer_010_func_002(free_null_pointer_010_gbl_dst,str2); free_null_pointer_010_func_003(); } void free_null_pointer_010_func_003() { int i; while(SET_MEM) { for(i=0;i&lt;5;i++) { free(free_null_pointer_010_gbl_dst[i]); free_null_pointer_010_gbl_dst[i] = NULL; } break; } while(SET_MEM == 0) { free(free_null_pointer_010_gbl_dst); free_null_pointer_010_gbl_dst = NULL;/*ERROR:Freeing a NULL pointer*/ break; } } define SET_MEM 0 void free_null_pointer_010_func_001() { int i; { while(SET_MEM) { free_null_pointer_010_gbl_dst = (char**) malloc(5*sizeof(char*)); for(i=0;i&lt;5;i++) { free_null_pointer_010_gbl_dst[i]=(char*) malloc(15*sizeof(char)); } break; } } }</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/free_null_pointer.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/free_null_pointer.c</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -676,14 +676,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/free_null_pointer.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/free_null_pointer.c</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,14 +698,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/free_null_pointer.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/free_null_pointer.c</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -720,14 +720,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/free_null_pointer.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/free_null_pointer.c</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>typedef struct { double *p1; double *p2; double *p3; } free_null_pointer_014_s_001; int *free_null_pointer_002_gbl_ptr = NULL; char **free_null_pointer_010_gbl_dst=NULL; static unsigned char a =INDEX; char * free_null_pointer_005_gbl_ptr; long ** free_null_pointer_007_gbl_doubleptr; enum {min_buffer = 0 , max_buffer = 5 }; static unsigned int min=min_buffer+2; static unsigned int max=max_buffer+2; char **free_null_pointer_009dst; static free_null_pointer_011_u_001 *u; free_null_pointer_014_s_001 *free_null_pointer_014_gbl_s=NULL; extern volatile int vflag; void free_null_pointer_014 () { free_null_pointer_014_func_001(1); free_null_pointer_014_func_002(1); free_null_pointer_014_func_003(1); } void free_null_pointer_014_func_001(int flag) { int i; if(flag ==1) { for (i=1;i&lt;1;i++) { free_null_pointer_014_gbl_s = malloc(sizeof(free_null_pointer_014_s_001)); free_null_pointer_014_gbl_s-&gt;p1 = malloc(sizeof(double)); free_null_pointer_014_gbl_s-&gt;p2 = malloc(sizeof(double)); free_null_pointer_014_gbl_s-&gt;p3 = malloc(sizeof(double)); } } } void free_null_pointer_014_func_003(int flag) { int i; if (flag ==1) { for (i=1;i&lt;1;i++) { free(free_null_pointer_014_gbl_s-&gt;p1); free(free_null_pointer_014_gbl_s-&gt;p2); free(free_null_pointer_014_gbl_s-&gt;p3); } for (i=0;i&lt;1;i++) { free(free_null_pointer_014_gbl_s);/* Tool should detect this line as error *//*ERROR:Freeing a NULL pointer*/ } } } void free_null_pointer_014_func_002(int flag) { static double arr[3]={10.0,20.0,30.0}; int i; if (flag ==1) { for (i=0;i&lt;1;i++) { *(free_null_pointer_014_gbl_s-&gt;p1) = arr[0]; *(free_null_pointer_014_gbl_s-&gt;p2) = arr[1]; *(free_null_pointer_014_gbl_s-&gt;p3) = arr[2]; } } }</t>
+          <t>typedef struct { double *p1; double *p2; double *p3; } free_null_pointer_014_s_001; int *free_null_pointer_002_gbl_ptr = NULL; char **free_null_pointer_010_gbl_dst=NULL; static unsigned char a =INDEX; char * free_null_pointer_005_gbl_ptr; long ** free_null_pointer_007_gbl_doubleptr; enum {min_buffer = 0 , max_buffer = 5 }; static unsigned int min=min_buffer+2; static unsigned int max=max_buffer+2; char **free_null_pointer_009dst; static free_null_pointer_011_u_001 *u; free_null_pointer_014_s_001 *free_null_pointer_014_gbl_s=NULL; extern volatile int vflag; void free_null_pointer_014 () { free_null_pointer_014_func_001(1); free_null_pointer_014_func_002(1); free_null_pointer_014_func_003(1); } void free_null_pointer_014_func_002(int flag) { static double arr[3]={10.0,20.0,30.0}; int i; if (flag ==1) { for (i=0;i&lt;1;i++) { *(free_null_pointer_014_gbl_s-&gt;p1) = arr[0]; *(free_null_pointer_014_gbl_s-&gt;p2) = arr[1]; *(free_null_pointer_014_gbl_s-&gt;p3) = arr[2]; } } } void free_null_pointer_014_func_001(int flag) { int i; if(flag ==1) { for (i=1;i&lt;1;i++) { free_null_pointer_014_gbl_s = malloc(sizeof(free_null_pointer_014_s_001)); free_null_pointer_014_gbl_s-&gt;p1 = malloc(sizeof(double)); free_null_pointer_014_gbl_s-&gt;p2 = malloc(sizeof(double)); free_null_pointer_014_gbl_s-&gt;p3 = malloc(sizeof(double)); } } } void free_null_pointer_014_func_003(int flag) { int i; if (flag ==1) { for (i=1;i&lt;1;i++) { free(free_null_pointer_014_gbl_s-&gt;p1); free(free_null_pointer_014_gbl_s-&gt;p2); free(free_null_pointer_014_gbl_s-&gt;p3); } for (i=0;i&lt;1;i++) { free(free_null_pointer_014_gbl_s);/* Tool should detect this line as error *//*ERROR:Freeing a NULL pointer*/ } } }</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
